--- a/AtchisonRegime/Outputs/USA/USA_Size_Tilt/df_regSummary_USA_Size_Tilt.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Size_Tilt/df_regSummary_USA_Size_Tilt.xlsx
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>1.427856165170456</v>
+        <v>1.180255717123087</v>
       </c>
       <c r="H2" t="n">
-        <v>3.338090341682212</v>
+        <v>3.648201252015532</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.88900426378396</v>
+        <v>-8.47616175672427</v>
       </c>
       <c r="J2" t="n">
         <v>7.79885715856029</v>
       </c>
       <c r="K2" t="n">
-        <v>31.70731707317073</v>
+        <v>32.25806451612903</v>
       </c>
       <c r="L2" t="n">
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1514102785121009</v>
+        <v>0.123231555519747</v>
       </c>
       <c r="O2" t="n">
         <v>-0.0119688944570685</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3297869389997989</v>
+        <v>0.2556739569809678</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>7.56280518804586</v>
       </c>
       <c r="K3" t="n">
-        <v>21.13821138211382</v>
+        <v>20.96774193548387</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>6.989405251611849</v>
       </c>
       <c r="K4" t="n">
-        <v>21.13821138211382</v>
+        <v>20.96774193548387</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>9.52544316828399</v>
       </c>
       <c r="K5" t="n">
-        <v>26.01626016260163</v>
+        <v>25.80645161290322</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
